--- a/backend/scripts/slt_source/AGC_SLT_Calendar_Master_2026-2027.xlsx
+++ b/backend/scripts/slt_source/AGC_SLT_Calendar_Master_2026-2027.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amirqualitymeatsinc-my.sharepoint.com/personal/garima_singh_amirgc_com/Documents/Desktop/SLT Tracker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amirqualitymeatsinc-my.sharepoint.com/personal/sandy_williams_amirgc_com/Documents/3. SLT Tracker/SLT Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{48F7B48D-FC8D-487F-8C51-448DEE5F4016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ECC078B-8CDD-4A66-A8ED-FB561E4E5A25}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E4D7308-7347-47BF-A294-0D892505F4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Master Calendar" sheetId="2" r:id="rId2"/>
     <sheet name="Weekly Review" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="Lists" sheetId="6" state="hidden" r:id="rId4"/>
+    <sheet name="Lists" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="177">
   <si>
     <t>Executive Calendar Draft – How to Use</t>
   </si>
@@ -183,6 +183,9 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>September</t>
+  </si>
+  <si>
     <t>Company Performance in Lieu of Town Hall</t>
   </si>
   <si>
@@ -192,9 +195,6 @@
     <t>Tom</t>
   </si>
   <si>
-    <t>September</t>
-  </si>
-  <si>
     <t>Monthly Coldbox Meeting</t>
   </si>
   <si>
@@ -210,12 +210,355 @@
     <t>Tony</t>
   </si>
   <si>
-    <t>Hold the Date for Possible CFO Board Presentation</t>
+    <t>Strategy Meetings - Day 1 (Rawley Resort Spa &amp; Marina)</t>
+  </si>
+  <si>
+    <t>Strategy Meetings - Day 2 (Rawley Resort Spa &amp; Marina)</t>
+  </si>
+  <si>
+    <t>CFO Board Presentation - 11:00AM</t>
   </si>
   <si>
     <t>October</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Opens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CTPP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> Chicken</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Access Qty =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 24,212,000 kg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>/ Eviscerated equivalent 
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Opens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CUSMA </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Chicken</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Access Qty = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>57,570,000 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Eviscerated equivalent
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Opens </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">- WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Chicken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Chicken Parts</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Access Qty = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>39,843,700 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Eviscerated equivalent
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Opens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Turkey </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>&amp; Turkey Products</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The greater of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>5,588,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> eviscerated equivalent or 3.5% of the previous year's production quota.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRQ Application</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> Opens - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Beef </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>and Veal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Access quantity -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 76,409,000 kg</t>
+    </r>
+  </si>
+  <si>
+    <t>CHFCA - Halal Audit</t>
+  </si>
+  <si>
+    <t>FSQA</t>
+  </si>
+  <si>
+    <t>Enid</t>
+  </si>
+  <si>
+    <t>Sierra Audit</t>
+  </si>
+  <si>
+    <t>Oct 6-8, 2026</t>
+  </si>
+  <si>
+    <t>CPEP Meetings - Calgary</t>
+  </si>
+  <si>
+    <t>Tom Attending</t>
+  </si>
+  <si>
+    <t>Thanksgiving Statuatory Holiday</t>
+  </si>
+  <si>
+    <t>People / HR</t>
+  </si>
+  <si>
+    <t>Gene</t>
+  </si>
+  <si>
+    <t>No SLT Meeting</t>
+  </si>
+  <si>
+    <t>David Attending In-Person</t>
+  </si>
+  <si>
     <t>Oct 17-21, 2026</t>
   </si>
   <si>
@@ -225,19 +568,506 @@
     <t>CEO / CFO / VP OPS / PRESIDENT</t>
   </si>
   <si>
+    <t>Oct 26-28, 2026</t>
+  </si>
+  <si>
+    <t>Baader Trip (Monticello, NY, Harrisonbourg VA)</t>
+  </si>
+  <si>
+    <t>Adam, Alexander, Harpreet, Agnaldo</t>
+  </si>
+  <si>
+    <t>Oct 27-28, 2026</t>
+  </si>
+  <si>
+    <t>CFC Audit 
+A-198 to A-201 quota periods 
+(September 21, 2025 – May 2, 2026)</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Sherry</t>
+  </si>
+  <si>
+    <t>On-Site
+( A-198 to A-201 quota periods (September 21, 2025 – May 2, 2026)</t>
+  </si>
+  <si>
+    <t>VP of Poulet Rouge - Sharing 2027 Plans</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Michael J.</t>
+  </si>
+  <si>
+    <t>Jason Snowy &amp; Anna (Popeyes) at AQM</t>
+  </si>
+  <si>
+    <t>Pro-Cert Organic Audit</t>
+  </si>
+  <si>
+    <r>
+      <t>90-Day Priorities (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>30-day Check-in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>3:30pm - 4:30pm</t>
+  </si>
+  <si>
+    <t>Oct 29-30, 2026</t>
+  </si>
+  <si>
+    <t>Edmonton Trip - Customer Appointments</t>
+  </si>
+  <si>
+    <t>Dave C/ Adam A.</t>
+  </si>
+  <si>
     <t>November</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">for SLT Review </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>- CTPP Chicken</t>
+    </r>
+  </si>
+  <si>
+    <t>Timeline as per SOP (Harsha)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>for SLT Review</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CUSMA Chicken</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>for SLT Review</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - WTO Chicken &amp; Chicken Parts</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">for SLT Review </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">- WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Turkey</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Turkey Products</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRQ Application</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> for SLT Review - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Beef </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>and Veal</t>
+    </r>
+  </si>
+  <si>
     <t>OMAFA Audit - Arthur</t>
   </si>
   <si>
-    <t>FSQA</t>
-  </si>
-  <si>
     <t>Montasser Abdelkodouss</t>
   </si>
   <si>
     <t>Plant Readiness</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Deadline</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CTPP Chicken</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Access Qty = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>24,212,000 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Eviscerated equivalent 
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Deadline</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CUSMA Chicken</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Access Qty =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 57,570,000 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Eviscerated equivalent
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Deadline </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>- WTO Chicken &amp; Chicken Parts</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Access Qty = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>39,843,700 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3" tint="0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Eviscerated equivalent
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Deadline </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">- WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Turkey</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Turkey Products</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The greater of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>5,588,000 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> eviscerated equivalent or 3.5% of the previous year's production quota. Return Deadline </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRQ Application</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> Deadline - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">WTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Beef </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>and Veal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Access quantity -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 76,409,000 kg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>90-Day Priorities (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>60-day Check-in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>December</t>
@@ -256,13 +1086,30 @@
     <t>Arthur Go-Live Date</t>
   </si>
   <si>
-    <t>Sherry</t>
-  </si>
-  <si>
     <t>Confirm readiness from all gate owners.</t>
   </si>
   <si>
     <t>Amir Year-End Gala</t>
+  </si>
+  <si>
+    <r>
+      <t>90-Day Priorities (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>90-day Review</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>January</t>
@@ -275,9 +1122,117 @@
     <t>February</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Opens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CTPP </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Turkey</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Access Qty =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 3,606,000 kg / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Eviscerated equivalent
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
     <t>March</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">TRQ Application </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Deadline </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> - CTPP </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Turkey</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Access Qty =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 3,606,000 kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="8"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Eviscerated equivalent
+(Application Ref Period Sept 1 - Aug 31)</t>
+    </r>
+  </si>
+  <si>
     <t>April</t>
   </si>
   <si>
@@ -359,9 +1314,6 @@
     <t>Ready</t>
   </si>
   <si>
-    <t>People / HR</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -380,9 +1332,6 @@
     <t>At Risk</t>
   </si>
   <si>
-    <t>Compliance</t>
-  </si>
-  <si>
     <t>CFO / Finance</t>
   </si>
   <si>
@@ -410,16 +1359,10 @@
     <t>Strategy</t>
   </si>
   <si>
-    <t>Customer</t>
+    <t>Operations / Finance</t>
   </si>
   <si>
     <t>Communication</t>
-  </si>
-  <si>
-    <t>Strategy Meetings - Day 1 (Rawley Resort Spa &amp; Marina)</t>
-  </si>
-  <si>
-    <t>Strategy Meetings - Day 2 (Rawley Resort Spa &amp; Marina)</t>
   </si>
 </sst>
 </file>
@@ -429,7 +1372,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -470,6 +1413,116 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -514,7 +1567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -570,6 +1623,69 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -580,32 +1696,9 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="37">
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -660,7 +1753,186 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -676,10 +1948,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MasterCalendarTable" displayName="MasterCalendarTable" ref="A2:M104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MasterCalendarTable" displayName="MasterCalendarTable" ref="A2:M130">
   <tableColumns count="13">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Event Date" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Event Date" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Event / Deadline"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Category"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Executive(s)"/>
@@ -846,25 +2118,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="33.65" customHeight="1">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+    </row>
+    <row r="3" spans="1:8" ht="33.6" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -872,7 +2144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="33.65" customHeight="1">
+    <row r="4" spans="1:8" ht="33.6" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,7 +2152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="33.65" customHeight="1">
+    <row r="5" spans="1:8" ht="33.6" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -888,7 +2160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33.65" customHeight="1">
+    <row r="6" spans="1:8" ht="33.6" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -896,7 +2168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="33.65" customHeight="1">
+    <row r="7" spans="1:8" ht="33.6" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -914,40 +2186,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M104"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:M130"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" style="14" customWidth="1"/>
-    <col min="3" max="3" width="46.9140625" customWidth="1"/>
-    <col min="4" max="4" width="17.4140625" customWidth="1"/>
+    <col min="3" max="3" width="46.875" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="30.25" customWidth="1"/>
     <col min="8" max="8" width="14" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="17.4140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.75" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="40" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="13" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="6.125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.75" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.4" customHeight="1">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+    </row>
+    <row r="2" spans="1:13" ht="26.45" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -1016,11 +2289,11 @@
       <c r="K3" s="7"/>
       <c r="L3" s="9">
         <f t="shared" ref="L3:L8" ca="1" si="0">IF(B3="","",B3-TODAY())</f>
-        <v>-63</v>
+        <v>-69</v>
       </c>
       <c r="M3" s="9">
         <f t="shared" ref="M3:M8" ca="1" si="1">IF(I3="","",I3-TODAY())</f>
-        <v>-65</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
@@ -1053,11 +2326,11 @@
       <c r="K4" s="7"/>
       <c r="L4" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>-61</v>
+        <v>-67</v>
       </c>
       <c r="M4" s="9">
         <f t="shared" ca="1" si="1"/>
-        <v>-63</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
@@ -1088,11 +2361,11 @@
       <c r="K5" s="11"/>
       <c r="L5" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>-57</v>
+        <v>-63</v>
       </c>
       <c r="M5" s="9">
         <f t="shared" ca="1" si="1"/>
-        <v>-61</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
@@ -1123,11 +2396,11 @@
       <c r="K6" s="11"/>
       <c r="L6" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>-56</v>
+        <v>-62</v>
       </c>
       <c r="M6" s="9">
         <f t="shared" ca="1" si="1"/>
-        <v>-58</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
@@ -1158,173 +2431,173 @@
       <c r="K7" s="11"/>
       <c r="L7" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>-55</v>
+        <v>-61</v>
       </c>
       <c r="M7" s="9">
         <f t="shared" ca="1" si="1"/>
-        <v>-58</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="20">
+        <v>46269</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="12">
+      <c r="G8" s="19"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21">
+        <v>46261</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="22">
+        <f t="shared" ca="1" si="0"/>
+        <v>-53</v>
+      </c>
+      <c r="M8" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A9" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="20">
+        <v>46267</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21">
+        <v>46266</v>
+      </c>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="22">
+        <f t="shared" ref="L9:L45" ca="1" si="2">IF(B9="","",B9-TODAY())</f>
+        <v>-55</v>
+      </c>
+      <c r="M9" s="22">
+        <f t="shared" ref="M9:M45" ca="1" si="3">IF(I9="","",I9-TODAY())</f>
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A10" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="20">
+        <v>46273</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21">
         <v>46269</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>-49</v>
+      </c>
+      <c r="M10" s="22">
+        <f t="shared" ca="1" si="3"/>
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A11" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="B11" s="20">
+        <v>46280</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8">
-        <v>46261</v>
-      </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>-47</v>
-      </c>
-      <c r="M8" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>-55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="E11" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="12">
-        <v>46267</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8">
-        <v>46266</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="9">
-        <f t="shared" ref="L9:L20" ca="1" si="2">IF(B9="","",B9-TODAY())</f>
-        <v>-49</v>
-      </c>
-      <c r="M9" s="9">
-        <f t="shared" ref="M9:M20" ca="1" si="3">IF(I9="","",I9-TODAY())</f>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="12">
-        <v>46273</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8">
-        <v>46269</v>
-      </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="9">
+      <c r="G11" s="19"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21">
+        <v>46275</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>-43</v>
-      </c>
-      <c r="M10" s="9">
+        <v>-42</v>
+      </c>
+      <c r="M11" s="22">
         <f t="shared" ca="1" si="3"/>
         <v>-47</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="7" t="s">
+    <row r="12" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A12" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="20">
+        <v>46281</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="12">
-        <v>46280</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8">
-        <v>46275</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="9">
-        <f t="shared" ca="1" si="2"/>
-        <v>-36</v>
-      </c>
-      <c r="M11" s="9">
-        <f t="shared" ca="1" si="3"/>
-        <v>-41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="12">
-        <v>46281</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="19"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8">
         <v>46275</v>
@@ -1333,33 +2606,33 @@
       <c r="K12" s="7"/>
       <c r="L12" s="9">
         <f t="shared" ca="1" si="2"/>
-        <v>-35</v>
+        <v>-41</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" ca="1" si="3"/>
-        <v>-41</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="20">
         <v>46295</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="7"/>
+      <c r="G13" s="19"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="7"/>
@@ -1367,61 +2640,57 @@
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
     </row>
-    <row r="14" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="12">
-        <v>46301</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="7" t="s">
+    <row r="14" spans="1:13" s="10" customFormat="1" ht="38.450000000000003" customHeight="1">
+      <c r="A14" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="20">
+        <v>46296</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="7"/>
+      <c r="E14" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>54</v>
+      </c>
       <c r="H14" s="8"/>
-      <c r="I14" s="8">
-        <v>46301</v>
-      </c>
+      <c r="I14" s="8"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="9">
-        <f t="shared" ca="1" si="2"/>
-        <v>-15</v>
-      </c>
-      <c r="M14" s="9">
-        <f t="shared" ca="1" si="3"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A15" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="B15" s="20">
+        <v>46296</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="F15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>56</v>
+      </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="7"/>
@@ -1429,26 +2698,28 @@
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
     </row>
-    <row r="16" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="12">
-        <v>46329</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="7" t="s">
+    <row r="16" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="20">
+        <v>46296</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="7"/>
+      <c r="E16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>58</v>
+      </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="7"/>
@@ -1456,63 +2727,57 @@
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
     </row>
-    <row r="17" spans="1:13" s="10" customFormat="1" ht="28">
-      <c r="A17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="12">
-        <v>46330</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>58</v>
+    <row r="17" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A17" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="20">
+        <v>46296</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>60</v>
       </c>
       <c r="H17" s="8"/>
-      <c r="I17" s="8">
-        <v>46515</v>
-      </c>
+      <c r="I17" s="8"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="9">
-        <f t="shared" ca="1" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="M17" s="9">
-        <f t="shared" ca="1" si="3"/>
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="10" customFormat="1">
-      <c r="A18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="12">
-        <v>46330</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="7"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A18" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="20">
+        <v>46296</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>62</v>
+      </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
       <c r="J18" s="7"/>
@@ -1520,99 +2785,85 @@
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
     </row>
-    <row r="19" spans="1:13" s="10" customFormat="1">
-      <c r="A19" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="12">
-        <v>46357</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="7" t="s">
+    <row r="19" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A19" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="20">
+        <v>46301</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8">
-        <v>46540</v>
-      </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" ca="1" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="M19" s="9">
-        <f t="shared" ca="1" si="3"/>
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="10" customFormat="1" ht="28">
-      <c r="A20" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="12">
-        <v>46359</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>58</v>
+      <c r="E20" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="9">
-        <f t="shared" ca="1" si="2"/>
-        <v>43</v>
-      </c>
-      <c r="M20" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="10" customFormat="1" ht="40.25" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="12">
-        <v>46360</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>58</v>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+    </row>
+    <row r="21" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A21" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="20">
+        <v>46307</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>73</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -1621,84 +2872,78 @@
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
     </row>
-    <row r="22" spans="1:13" s="10" customFormat="1" ht="28">
-      <c r="A22" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="12">
-        <v>46368</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="7" t="s">
+    <row r="22" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A22" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="20">
+        <v>46315</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>65</v>
+      <c r="E22" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="9">
-        <f t="shared" ref="L22:L52" ca="1" si="4">IF(B22="","",B22-TODAY())</f>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+    </row>
+    <row r="23" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A23" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="M22" s="9" t="str">
-        <f t="shared" ref="M22:M52" ca="1" si="5">IF(I22="","",I22-TODAY())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="10" customFormat="1">
-      <c r="A23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="12">
-        <v>46368</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="B23" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="7"/>
+      <c r="E23" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="19"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="9">
-        <f t="shared" ca="1" si="4"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M23" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:13" s="10" customFormat="1">
-      <c r="A24" s="16">
-        <v>2027</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="7"/>
+      <c r="B24" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="7"/>
@@ -1706,706 +2951,868 @@
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
     </row>
-    <row r="25" spans="1:13" s="10" customFormat="1" ht="28">
+    <row r="25" spans="1:13" s="10" customFormat="1" ht="45" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>81</v>
+      </c>
       <c r="C25" s="7" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M25" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:13" s="10" customFormat="1">
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="B26" s="12">
+        <v>46323</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M26" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="10" customFormat="1">
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="B27" s="12">
+        <v>46323</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="G27" s="7"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M27" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:13" s="10" customFormat="1">
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="B28" s="12">
+        <v>46324</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="9" t="e">
-        <f ca="1">IF(#REF!="","",#REF!-TODAY())</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M28" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="10" customFormat="1">
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="B29" s="12">
+        <v>46324</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>92</v>
+      </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M29" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="10" customFormat="1">
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="G30" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M30" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="10" customFormat="1">
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="B31" s="12">
+        <v>46328</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M31" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:13" s="10" customFormat="1">
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="B32" s="12">
+        <v>46328</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M32" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="10" customFormat="1">
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A33" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="12">
+        <v>46328</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="G33" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M33" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="10" customFormat="1">
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="B34" s="12">
+        <v>46328</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M34" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:13" s="10" customFormat="1">
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="B35" s="12">
+        <v>46328</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>102</v>
+      </c>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M35" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="10" customFormat="1">
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="B36" s="12">
+        <v>46329</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M36" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:13" s="10" customFormat="1">
-      <c r="A37" s="7" t="str">
-        <f t="shared" ref="A37:A68" si="6">IF(B37="","",TEXT(B37,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+    </row>
+    <row r="37" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A37" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="12">
+        <v>46330</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="8">
+        <v>46515</v>
+      </c>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M37" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:13" s="10" customFormat="1">
-      <c r="A38" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="L37" s="9">
+        <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="M37" s="9">
+        <f t="shared" ca="1" si="3"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="12">
+        <v>46341</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>107</v>
+      </c>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
-      <c r="L38" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M38" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="10" customFormat="1">
-      <c r="A39" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A39" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="24">
+        <v>46341</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="25" t="s">
+        <v>109</v>
+      </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
-      <c r="L39" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M39" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:13" s="10" customFormat="1">
-      <c r="A40" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A40" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="24">
+        <v>46341</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>111</v>
+      </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
-      <c r="L40" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M40" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="10" customFormat="1">
-      <c r="A41" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M41" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="10" customFormat="1">
-      <c r="A42" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M42" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:13" s="10" customFormat="1">
-      <c r="A43" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="1:13" s="33" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A41" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="29">
+        <v>46341</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+    </row>
+    <row r="42" spans="1:13" s="33" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A42" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="37">
+        <v>46341</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+    </row>
+    <row r="43" spans="1:13" s="33" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A43" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="12">
+        <v>46350</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
-      <c r="L43" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M43" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:13" s="10" customFormat="1">
-      <c r="A44" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A44" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" s="12">
+        <v>46357</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
+      <c r="I44" s="8">
+        <v>46540</v>
+      </c>
       <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M44" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="10" customFormat="1">
-      <c r="A45" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
+      <c r="K44" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="L44" s="9">
+        <f t="shared" ca="1" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="M44" s="9">
+        <f t="shared" ca="1" si="3"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A45" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="12">
+        <v>46359</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
-      <c r="L45" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+      <c r="L45" s="9">
+        <f t="shared" ca="1" si="2"/>
+        <v>37</v>
       </c>
       <c r="M45" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="10" customFormat="1">
-      <c r="A46" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A46" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="12">
+        <v>46360</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M46" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:13" s="10" customFormat="1">
-      <c r="A47" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+    </row>
+    <row r="47" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A47" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="12">
+        <v>46368</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>122</v>
+      </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
+      <c r="L47" s="9">
+        <f t="shared" ref="L47:L78" ca="1" si="4">IF(B47="","",B47-TODAY())</f>
+        <v>46</v>
       </c>
       <c r="M47" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="10" customFormat="1">
-      <c r="A48" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+        <f t="shared" ref="M47:M78" ca="1" si="5">IF(I47="","",I47-TODAY())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A48" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="12">
+        <v>46368</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="G48" s="7"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
-      <c r="L48" s="9" t="str">
+      <c r="L48" s="9">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>46</v>
       </c>
       <c r="M48" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:13" s="10" customFormat="1">
-      <c r="A49" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
+    <row r="49" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A49" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="12">
+        <v>46378</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="G49" s="7"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
-      <c r="L49" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M49" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:13" s="10" customFormat="1">
-      <c r="A50" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+    </row>
+    <row r="50" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A50" s="16">
+        <v>2027</v>
+      </c>
+      <c r="B50" s="26"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
-      <c r="L50" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M50" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="10" customFormat="1">
-      <c r="A51" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+    </row>
+    <row r="51" spans="1:13" s="10" customFormat="1" ht="27.6">
+      <c r="A51" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="12">
+        <v>46413</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="9" t="str">
+      <c r="L51" s="9">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>91</v>
       </c>
       <c r="M51" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:13" s="10" customFormat="1">
-      <c r="A52" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B52" s="12"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="9" t="str">
+    <row r="52" spans="1:13" s="10" customFormat="1" ht="52.9">
+      <c r="A52" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="29">
+        <v>46419</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="32">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M52" s="9" t="str">
+        <v>97</v>
+      </c>
+      <c r="M52" s="32" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:13" s="10" customFormat="1">
-      <c r="A53" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
+    <row r="53" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A53" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="29">
+        <v>46461</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="30" t="s">
+        <v>132</v>
+      </c>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="9" t="str">
-        <f t="shared" ref="L53:L84" ca="1" si="7">IF(B53="","",B53-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M53" s="9" t="str">
-        <f t="shared" ref="M53:M84" ca="1" si="8">IF(I53="","",I53-TODAY())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:13" s="10" customFormat="1">
-      <c r="A54" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B54" s="12"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+    </row>
+    <row r="54" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A54" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" s="15"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -2415,19 +3822,18 @@
       <c r="I54" s="8"/>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
+      <c r="L54" s="9" t="e">
+        <f ca="1">IF(#REF!="","",#REF!-TODAY())</f>
+        <v>#REF!</v>
       </c>
       <c r="M54" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="10" customFormat="1">
-      <c r="A55" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1">
+      <c r="A55" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="7"/>
@@ -2440,18 +3846,17 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M55" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="1:13" s="10" customFormat="1">
-      <c r="A56" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="A56" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="7"/>
@@ -2464,18 +3869,17 @@
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
       <c r="L56" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M56" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="1:13" s="10" customFormat="1">
-      <c r="A57" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="A57" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="7"/>
@@ -2488,18 +3892,17 @@
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M57" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="58" spans="1:13" s="10" customFormat="1">
-      <c r="A58" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="A58" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="7"/>
@@ -2512,18 +3915,17 @@
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M58" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="1:13" s="10" customFormat="1">
-      <c r="A59" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="A59" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="7"/>
@@ -2536,18 +3938,17 @@
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M59" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="1:13" s="10" customFormat="1">
-      <c r="A60" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="A60" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="7"/>
@@ -2560,18 +3961,17 @@
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
       <c r="L60" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M60" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="10" customFormat="1">
-      <c r="A61" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="10" customFormat="1" ht="37.9" customHeight="1">
+      <c r="A61" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="7"/>
@@ -2584,18 +3984,17 @@
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M61" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="62" spans="1:13" s="10" customFormat="1">
-      <c r="A62" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="A62" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="B62" s="12"/>
       <c r="C62" s="7"/>
@@ -2608,17 +4007,17 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M62" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="63" spans="1:13" s="10" customFormat="1">
       <c r="A63" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A63:A94" si="6">IF(B63="","",TEXT(B63,"mmmm"))</f>
         <v/>
       </c>
       <c r="B63" s="12"/>
@@ -2632,11 +4031,11 @@
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M63" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
@@ -2656,11 +4055,11 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M64" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
@@ -2680,11 +4079,11 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M65" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
@@ -2704,11 +4103,11 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M66" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
@@ -2728,11 +4127,11 @@
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M67" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
@@ -2752,17 +4151,17 @@
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M68" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:13" s="10" customFormat="1">
       <c r="A69" s="7" t="str">
-        <f t="shared" ref="A69:A100" si="9">IF(B69="","",TEXT(B69,"mmmm"))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B69" s="12"/>
@@ -2776,17 +4175,17 @@
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M69" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:13" s="10" customFormat="1">
       <c r="A70" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B70" s="12"/>
@@ -2800,17 +4199,17 @@
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M70" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="1:13" s="10" customFormat="1">
       <c r="A71" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B71" s="12"/>
@@ -2824,17 +4223,17 @@
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M71" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="1:13" s="10" customFormat="1">
       <c r="A72" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B72" s="12"/>
@@ -2848,17 +4247,17 @@
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M72" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:13" s="10" customFormat="1">
       <c r="A73" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B73" s="12"/>
@@ -2872,17 +4271,17 @@
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M73" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="74" spans="1:13" s="10" customFormat="1">
       <c r="A74" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B74" s="12"/>
@@ -2896,17 +4295,17 @@
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M74" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:13" s="10" customFormat="1">
       <c r="A75" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B75" s="12"/>
@@ -2920,17 +4319,17 @@
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
       <c r="L75" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M75" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:13" s="10" customFormat="1">
       <c r="A76" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B76" s="12"/>
@@ -2944,17 +4343,17 @@
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
       <c r="L76" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M76" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:13" s="10" customFormat="1">
       <c r="A77" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B77" s="12"/>
@@ -2968,17 +4367,17 @@
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M77" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:13" s="10" customFormat="1">
       <c r="A78" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B78" s="12"/>
@@ -2992,17 +4391,17 @@
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
       <c r="L78" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="M78" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:13" s="10" customFormat="1">
       <c r="A79" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B79" s="12"/>
@@ -3016,17 +4415,17 @@
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ref="L79:L110" ca="1" si="7">IF(B79="","",B79-TODAY())</f>
         <v/>
       </c>
       <c r="M79" s="9" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ref="M79:M110" ca="1" si="8">IF(I79="","",I79-TODAY())</f>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:13" s="10" customFormat="1">
       <c r="A80" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B80" s="12"/>
@@ -3050,7 +4449,7 @@
     </row>
     <row r="81" spans="1:13" s="10" customFormat="1">
       <c r="A81" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B81" s="12"/>
@@ -3074,7 +4473,7 @@
     </row>
     <row r="82" spans="1:13" s="10" customFormat="1">
       <c r="A82" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B82" s="12"/>
@@ -3098,7 +4497,7 @@
     </row>
     <row r="83" spans="1:13" s="10" customFormat="1">
       <c r="A83" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="B83" s="12"/>
@@ -3120,554 +4519,1261 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="4" t="str">
+    <row r="84" spans="1:13" s="10" customFormat="1">
+      <c r="A84" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B84" s="12"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M84" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:13" s="10" customFormat="1">
+      <c r="A85" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B85" s="12"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M85" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:13" s="10" customFormat="1">
+      <c r="A86" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B86" s="12"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M86" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:13" s="10" customFormat="1">
+      <c r="A87" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B87" s="12"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M87" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:13" s="10" customFormat="1">
+      <c r="A88" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B88" s="12"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="7"/>
+      <c r="L88" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M88" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:13" s="10" customFormat="1">
+      <c r="A89" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B89" s="12"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M89" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:13" s="10" customFormat="1">
+      <c r="A90" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B90" s="12"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M90" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:13" s="10" customFormat="1">
+      <c r="A91" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B91" s="12"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M91" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:13" s="10" customFormat="1">
+      <c r="A92" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B92" s="12"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M92" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:13" s="10" customFormat="1">
+      <c r="A93" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B93" s="12"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M93" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:13" s="10" customFormat="1">
+      <c r="A94" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B94" s="12"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M94" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:13" s="10" customFormat="1">
+      <c r="A95" s="7" t="str">
+        <f t="shared" ref="A95:A126" si="9">IF(B95="","",TEXT(B95,"mmmm"))</f>
+        <v/>
+      </c>
+      <c r="B95" s="12"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M95" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:13" s="10" customFormat="1">
+      <c r="A96" s="7" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="6" t="str">
+      <c r="B96" s="12"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="7"/>
+      <c r="L96" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
-      <c r="M84" s="6" t="str">
+      <c r="M96" s="9" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="4" t="str">
+    <row r="97" spans="1:13" s="10" customFormat="1">
+      <c r="A97" s="7" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="5"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="6" t="str">
-        <f t="shared" ref="L85:L104" ca="1" si="10">IF(B85="","",B85-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M85" s="6" t="str">
-        <f t="shared" ref="M85:M104" ca="1" si="11">IF(I85="","",I85-TODAY())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="4" t="str">
+      <c r="B97" s="12"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M97" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="10" customFormat="1">
+      <c r="A98" s="7" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="6" t="str">
+      <c r="B98" s="12"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M98" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:13" s="10" customFormat="1">
+      <c r="A99" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B99" s="12"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M99" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:13" s="10" customFormat="1">
+      <c r="A100" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B100" s="12"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M100" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="10" customFormat="1">
+      <c r="A101" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B101" s="12"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M101" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:13" s="10" customFormat="1">
+      <c r="A102" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B102" s="12"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M102" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:13" s="10" customFormat="1">
+      <c r="A103" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B103" s="12"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M103" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:13" s="10" customFormat="1">
+      <c r="A104" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B104" s="12"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M104" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:13" s="10" customFormat="1">
+      <c r="A105" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B105" s="12"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M105" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:13" s="10" customFormat="1">
+      <c r="A106" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B106" s="12"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="7"/>
+      <c r="K106" s="7"/>
+      <c r="L106" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M106" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:13" s="10" customFormat="1">
+      <c r="A107" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B107" s="12"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M107" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:13" s="10" customFormat="1">
+      <c r="A108" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B108" s="12"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M108" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:13" s="10" customFormat="1">
+      <c r="A109" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B109" s="12"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="9" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M109" s="9" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:13" s="10" customFormat="1">
+      <c r="A110" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B110" s="13"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="6" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="M110" s="6" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B111" s="13"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="6" t="str">
+        <f t="shared" ref="L111:L130" ca="1" si="10">IF(B111="","",B111-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M111" s="6" t="str">
+        <f t="shared" ref="M111:M130" ca="1" si="11">IF(I111="","",I111-TODAY())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="B112" s="13"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M86" s="6" t="str">
+      <c r="M112" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="4" t="str">
+    <row r="113" spans="1:13">
+      <c r="A113" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="6" t="str">
+      <c r="B113" s="13"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M87" s="6" t="str">
+      <c r="M113" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="4" t="str">
+    <row r="114" spans="1:13">
+      <c r="A114" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B88" s="13"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="6" t="str">
+      <c r="B114" s="13"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M88" s="6" t="str">
+      <c r="M114" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="4" t="str">
+    <row r="115" spans="1:13">
+      <c r="A115" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B89" s="13"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="6" t="str">
+      <c r="B115" s="13"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M89" s="6" t="str">
+      <c r="M115" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="4" t="str">
+    <row r="116" spans="1:13">
+      <c r="A116" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="6" t="str">
+      <c r="B116" s="13"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M90" s="6" t="str">
+      <c r="M116" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="4" t="str">
+    <row r="117" spans="1:13">
+      <c r="A117" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B91" s="13"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="6" t="str">
+      <c r="B117" s="13"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M91" s="6" t="str">
+      <c r="M117" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="4" t="str">
+    <row r="118" spans="1:13">
+      <c r="A118" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="6" t="str">
+      <c r="B118" s="13"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M92" s="6" t="str">
+      <c r="M118" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:13">
-      <c r="A93" s="4" t="str">
+    <row r="119" spans="1:13">
+      <c r="A119" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B93" s="13"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="6" t="str">
+      <c r="B119" s="13"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M93" s="6" t="str">
+      <c r="M119" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:13">
-      <c r="A94" s="4" t="str">
+    <row r="120" spans="1:13">
+      <c r="A120" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B94" s="13"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="6" t="str">
+      <c r="B120" s="13"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+      <c r="L120" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M94" s="6" t="str">
+      <c r="M120" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:13">
-      <c r="A95" s="4" t="str">
+    <row r="121" spans="1:13">
+      <c r="A121" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B95" s="13"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="6" t="str">
+      <c r="B121" s="13"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M95" s="6" t="str">
+      <c r="M121" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:13">
-      <c r="A96" s="4" t="str">
+    <row r="122" spans="1:13">
+      <c r="A122" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B96" s="13"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="5"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="6" t="str">
+      <c r="B122" s="13"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
+      <c r="L122" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M96" s="6" t="str">
+      <c r="M122" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:13">
-      <c r="A97" s="4" t="str">
+    <row r="123" spans="1:13">
+      <c r="A123" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B97" s="13"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="5"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="6" t="str">
+      <c r="B123" s="13"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M97" s="6" t="str">
+      <c r="M123" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:13">
-      <c r="A98" s="4" t="str">
+    <row r="124" spans="1:13">
+      <c r="A124" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B98" s="13"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="6" t="str">
+      <c r="B124" s="13"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+      <c r="L124" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M98" s="6" t="str">
+      <c r="M124" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:13">
-      <c r="A99" s="4" t="str">
+    <row r="125" spans="1:13">
+      <c r="A125" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="6" t="str">
+      <c r="B125" s="13"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+      <c r="L125" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M99" s="6" t="str">
+      <c r="M125" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:13">
-      <c r="A100" s="4" t="str">
+    <row r="126" spans="1:13">
+      <c r="A126" s="4" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="B100" s="13"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="6" t="str">
+      <c r="B126" s="13"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+      <c r="L126" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M100" s="6" t="str">
+      <c r="M126" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:13">
-      <c r="A101" s="4" t="str">
-        <f t="shared" ref="A101:A104" si="12">IF(B101="","",TEXT(B101,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="B101" s="13"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="6" t="str">
+    <row r="127" spans="1:13">
+      <c r="A127" s="4" t="str">
+        <f t="shared" ref="A127:A130" si="12">IF(B127="","",TEXT(B127,"mmmm"))</f>
+        <v/>
+      </c>
+      <c r="B127" s="13"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+      <c r="L127" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M101" s="6" t="str">
+      <c r="M127" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:13">
-      <c r="A102" s="4" t="str">
+    <row r="128" spans="1:13">
+      <c r="A128" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="5"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="6" t="str">
+      <c r="B128" s="13"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
+      <c r="L128" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M102" s="6" t="str">
+      <c r="M128" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:13">
-      <c r="A103" s="4" t="str">
+    <row r="129" spans="1:13">
+      <c r="A129" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="B103" s="13"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="4"/>
-      <c r="L103" s="6" t="str">
+      <c r="B129" s="13"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M103" s="6" t="str">
+      <c r="M129" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:13">
-      <c r="A104" s="4" t="str">
+    <row r="130" spans="1:13">
+      <c r="A130" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="B104" s="13"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="6" t="str">
+      <c r="B130" s="13"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="4"/>
+      <c r="K130" s="4"/>
+      <c r="L130" s="6" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="M104" s="6" t="str">
+      <c r="M130" s="6" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ddMcJgmhRZBbCt//ZJvrxmvu094EgduLatEh54s9sswkAQL2HAQAUInlM0OcAbXa2fuDRHZ5+L/xPut88aYDrA==" saltValue="hvrounK70cJxiwQamhsutg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="11" priority="5">
+  <conditionalFormatting sqref="A13:F18 A19:M30 A31:B35 D31:M35 A36:M37 A43:M51 A52:F53 H52:M53">
+    <cfRule type="expression" dxfId="36" priority="52">
+      <formula>#REF!="Include"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="51">
+      <formula>#REF!="High"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="50">
+      <formula>#REF!="At Risk"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="49">
       <formula>#REF!="Completed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42:F42">
+    <cfRule type="expression" dxfId="32" priority="13">
+      <formula>#REF!="Completed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="14">
       <formula>#REF!="At Risk"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="30" priority="15">
       <formula>#REF!="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="29" priority="16">
       <formula>#REF!="Include"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:F18">
-    <cfRule type="expression" dxfId="7" priority="1">
+  <conditionalFormatting sqref="A3:M12 G13:M18 A38:B41 G38:M42 A54 C54:M54 A55:M130">
+    <cfRule type="expression" dxfId="28" priority="76">
+      <formula>#REF!="Include"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="74">
+      <formula>#REF!="At Risk"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="73">
       <formula>#REF!="Completed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="25" priority="75">
+      <formula>#REF!="High"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31:C35">
+    <cfRule type="expression" dxfId="24" priority="6">
       <formula>#REF!="At Risk"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>#REF!="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="22" priority="8">
+      <formula>#REF!="Include"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="5">
+      <formula>#REF!="Completed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38:C41">
+    <cfRule type="expression" dxfId="20" priority="41">
+      <formula>#REF!="Completed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="42">
+      <formula>#REF!="At Risk"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="43">
+      <formula>#REF!="High"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="44">
       <formula>#REF!="Include"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:M12 G13:M13 A14:M17 G18:M18 A19:M27 A28 C28:M28 A29:M104">
-    <cfRule type="expression" dxfId="3" priority="29">
+  <conditionalFormatting sqref="D38:D41">
+    <cfRule type="expression" dxfId="16" priority="32">
+      <formula>#REF!="Include"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="31">
+      <formula>#REF!="High"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="30">
+      <formula>#REF!="At Risk"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="29">
       <formula>#REF!="Completed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="30">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:E41">
+    <cfRule type="expression" dxfId="12" priority="36">
+      <formula>#REF!="Include"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="34">
       <formula>#REF!="At Risk"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="31">
+    <cfRule type="expression" dxfId="10" priority="33">
+      <formula>#REF!="Completed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="35">
       <formula>#REF!="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="32">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38:F41">
+    <cfRule type="expression" dxfId="8" priority="37">
+      <formula>#REF!="Completed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="38">
+      <formula>#REF!="At Risk"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="39">
+      <formula>#REF!="High"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="40">
+      <formula>#REF!="Include"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G52:G53">
+    <cfRule type="expression" dxfId="4" priority="17">
+      <formula>#REF!="Completed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="18">
+      <formula>#REF!="At Risk"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="19">
+      <formula>#REF!="High"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>#REF!="Include"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3678,18 +5784,24 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{8DD1E3E2-073A-49DC-ACF9-71B663FCEFF8}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$40</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D12 D14:D17 D19:D1048576</xm:sqref>
+          <xm:sqref>D3:D12 D14:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{FE4F1806-0A05-4C11-A66A-83781F4925AC}">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$40</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E12 E14:E17 E19:E1048576</xm:sqref>
+          <xm:sqref>E3:E12 E19:E37 E43:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A7D1E36E-B4D2-480F-83D2-05A7CF10FCC4}">
+          <x14:formula1>
+            <xm:f>Lists!$D$2:$D$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>E14:E18 E38:E42</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3700,7 +5812,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -3720,32 +5832,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24" customHeight="1">
-      <c r="A1" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-    </row>
-    <row r="2" spans="1:20" ht="28">
+      <c r="A1" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+    </row>
+    <row r="2" spans="1:20" ht="27.6">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
@@ -3778,19 +5890,19 @@
         <v>21</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>22</v>
@@ -3802,12 +5914,12 @@
         <v>24</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="4" t="e" cm="1">
-        <f t="array" ref="A3">_xlfn._xlws.FILTER('Master Calendar'!A3:M104,'Master Calendar'!#REF!="Include","No items currently flagged for weekly review")</f>
+        <f t="array" ref="A3">_xlfn._xlws.FILTER('Master Calendar'!A3:M130,'Master Calendar'!#REF!="Include","No items currently flagged for weekly review")</f>
         <v>#REF!</v>
       </c>
       <c r="B3" s="4"/>
@@ -4655,92 +6767,92 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>27</v>
@@ -4751,55 +6863,55 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4809,7 +6921,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
@@ -4819,21 +6931,21 @@
     <row r="10" spans="1:6">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
@@ -4841,41 +6953,45 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="4" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
